--- a/data/Excel/GuLiStrikeRogueCards.xlsx
+++ b/data/Excel/GuLiStrikeRogueCards.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -249,6 +249,78 @@
   </si>
   <si>
     <t>两个GPU发射器；每单位1辉光网格+1光圈+18/6/0个独立随机短光粒（高/中/低画质）；每批1024单位槽、20480个GPU粒子容量，组件共享池化。</t>
+  </si>
+  <si>
+    <t>己方本局所有现有及后续重防号：增加射速；独立来源逐次乘算。</t>
+  </si>
+  <si>
+    <t>己方本局所有现有及后续重防号：极速机动；独立来源逐次乘算。</t>
+  </si>
+  <si>
+    <t>己方本局所有现有及后续重防号：增加导弹伤害；独立来源逐次乘算。</t>
+  </si>
+  <si>
+    <t>引用Commander/Soldiers.id；重防号WM01=2。</t>
+  </si>
+  <si>
+    <t>本局己方当前/后续重防号，换任指挥官保留，新战局清空。</t>
+  </si>
+  <si>
+    <t>有限正数。重防号当前默认6.0（实战宽约12.5米）；1.0为基础特效尺寸，光圈精灵直径约3.2米。统一缩放光圈、辉光和光粒，其他单位应单独适配。</t>
+  </si>
+  <si>
+    <t>RequiredCardIds</t>
+  </si>
+  <si>
+    <t>ExcludedCardIds</t>
+  </si>
+  <si>
+    <t>MaxAcquisitions</t>
+  </si>
+  <si>
+    <t>BonusCount</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>["04.01"]</t>
+  </si>
+  <si>
+    <t>04.01</t>
+  </si>
+  <si>
+    <t>WM01_MissilePod_Lv1</t>
+  </si>
+  <si>
+    <t>己方本局当前及后续重防号：重防导弹仓。解锁导弹技能与导弹仓，每队一次。</t>
+  </si>
+  <si>
+    <t>["Card.WM01.MissilePod.Title", "Card.WM01.MissilePod.Description"]</t>
+  </si>
+  <si>
+    <t>/Script/GuLiStrike.GuLiRogueCardMissilePodEffect</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Cards/Commander/WM01/MissilePod/Materials/MI_MissilePod_ModelComic_v1.MI_MissilePod_ModelComic_v1</t>
+  </si>
+  <si>
+    <t>05.01</t>
+  </si>
+  <si>
+    <t>WM01_RainSalvo_Lv1</t>
+  </si>
+  <si>
+    <t>己方本局当前及后续重防号：雨点攻势。每次Q的同时齐射数量加1，可重复叠加。</t>
+  </si>
+  <si>
+    <t>["Card.WM01.RainSalvo.Title", "Card.WM01.RainSalvo.Description"]</t>
+  </si>
+  <si>
+    <t>/Script/GuLiStrike.GuLiRogueCardMissileCountEffect</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Cards/Commander/WM01/RainSalvo/Materials/MI_RainSalvo_ModelComic_v1.MI_RainSalvo_ModelComic_v1</t>
   </si>
 </sst>
 </file>
@@ -650,6 +722,18 @@
       <c r="L1" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="M1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -688,6 +772,18 @@
       <c r="L2" t="s">
         <v>9</v>
       </c>
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -712,7 +808,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>15</v>
@@ -724,6 +820,18 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -735,7 +843,7 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -763,6 +871,18 @@
       </c>
       <c r="L4" t="s">
         <v>65</v>
+      </c>
+      <c r="M4" t="s">
+        <v>88</v>
+      </c>
+      <c r="N4" t="s">
+        <v>88</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -773,7 +893,7 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -801,6 +921,18 @@
       </c>
       <c r="L5" t="s">
         <v>65</v>
+      </c>
+      <c r="M5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" t="s">
+        <v>88</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -811,7 +943,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -839,6 +971,118 @@
       </c>
       <c r="L6" t="s">
         <v>65</v>
+      </c>
+      <c r="M6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N6" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" t="s">
+        <v>89</v>
+      </c>
+      <c r="N8" t="s">
+        <v>88</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -914,7 +1158,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -946,7 +1190,7 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -986,7 +1230,7 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">

--- a/data/Excel/GuLiStrikeRogueCards.xlsx
+++ b/data/Excel/GuLiStrikeRogueCards.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Cards/Commander/WM01/RainSalvo/Materials/MI_RainSalvo_ModelComic_v1.MI_RainSalvo_ModelComic_v1</t>
+  </si>
+  <si>
+    <t>己方本局当前及后续重防号：雨点攻势。完整齐射数量每次加1，基础1发，每队本局最多59次，单台上限60发。</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1046,7 @@
         <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1079,7 +1082,7 @@
         <v>88</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="P8">
         <v>1</v>

--- a/data/Excel/GuLiStrikeRogueCards.xlsx
+++ b/data/Excel/GuLiStrikeRogueCards.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -324,6 +324,12 @@
   </si>
   <si>
     <t>己方本局当前及后续重防号：雨点攻势。完整齐射数量每次加1，基础1发，每队本局最多59次，单台上限60发。</t>
+  </si>
+  <si>
+    <t>ArtworkId</t>
+  </si>
+  <si>
+    <t>整数，引用GuLiStrikeCardArtwork.xlsx/Artworks.id；导出为既有FrontMaterial，不在源表重复维护材质路径。</t>
   </si>
 </sst>
 </file>
@@ -714,7 +720,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>61</v>
@@ -764,7 +770,7 @@
         <v>13</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -863,8 +869,8 @@
       <c r="H4">
         <v>0.2</v>
       </c>
-      <c r="I4" t="s">
-        <v>56</v>
+      <c r="I4">
+        <v>1</v>
       </c>
       <c r="J4" t="s">
         <v>62</v>
@@ -913,8 +919,8 @@
       <c r="H5">
         <v>0.5</v>
       </c>
-      <c r="I5" t="s">
-        <v>57</v>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="J5" t="s">
         <v>62</v>
@@ -963,8 +969,8 @@
       <c r="H6">
         <v>0.2</v>
       </c>
-      <c r="I6" t="s">
-        <v>58</v>
+      <c r="I6">
+        <v>3</v>
       </c>
       <c r="J6" t="s">
         <v>62</v>
@@ -1013,8 +1019,8 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
-        <v>95</v>
+      <c r="I7">
+        <v>4</v>
       </c>
       <c r="J7" t="s">
         <v>62</v>
@@ -1063,8 +1069,8 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
-        <v>101</v>
+      <c r="I8">
+        <v>5</v>
       </c>
       <c r="J8" t="s">
         <v>62</v>
@@ -1174,10 +1180,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
